--- a/data/nzd0012/nzd0012.xlsx
+++ b/data/nzd0012/nzd0012.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB209"/>
+  <dimension ref="A1:AB210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18990,7 +18990,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>346.48</v>
+        <v>349.1</v>
       </c>
       <c r="C209" t="n">
         <v>352.66</v>
@@ -19032,7 +19032,7 @@
         <v>376.9</v>
       </c>
       <c r="P209" t="n">
-        <v>359.88</v>
+        <v>363.55</v>
       </c>
       <c r="Q209" t="n">
         <v>366.95</v>
@@ -19068,6 +19068,96 @@
         <v>371.73</v>
       </c>
       <c r="AB209" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>349.22</v>
+      </c>
+      <c r="C210" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="D210" t="n">
+        <v>355.31</v>
+      </c>
+      <c r="E210" t="n">
+        <v>346.91</v>
+      </c>
+      <c r="F210" t="n">
+        <v>333.68</v>
+      </c>
+      <c r="G210" t="n">
+        <v>347.53</v>
+      </c>
+      <c r="H210" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="I210" t="n">
+        <v>355.18</v>
+      </c>
+      <c r="J210" t="n">
+        <v>354.06</v>
+      </c>
+      <c r="K210" t="n">
+        <v>358.9</v>
+      </c>
+      <c r="L210" t="n">
+        <v>359.07</v>
+      </c>
+      <c r="M210" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="N210" t="n">
+        <v>351.65</v>
+      </c>
+      <c r="O210" t="n">
+        <v>383.64</v>
+      </c>
+      <c r="P210" t="n">
+        <v>362.77</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>370.71</v>
+      </c>
+      <c r="R210" t="n">
+        <v>369.14</v>
+      </c>
+      <c r="S210" t="n">
+        <v>365.92</v>
+      </c>
+      <c r="T210" t="n">
+        <v>365.76</v>
+      </c>
+      <c r="U210" t="n">
+        <v>363.96</v>
+      </c>
+      <c r="V210" t="n">
+        <v>362.44</v>
+      </c>
+      <c r="W210" t="n">
+        <v>365.74</v>
+      </c>
+      <c r="X210" t="n">
+        <v>364.07</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>368.91</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>361.03</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>368.05</v>
+      </c>
+      <c r="AB210" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19084,7 +19174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B211"/>
+  <dimension ref="A1:B212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21197,6 +21287,16 @@
       </c>
       <c r="B211" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -21365,28 +21465,28 @@
         <v>0.0363</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0830014183232165</v>
+        <v>0.07416700232689666</v>
       </c>
       <c r="J2" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K2" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002220276311982627</v>
+        <v>0.00179030665187152</v>
       </c>
       <c r="M2" t="n">
-        <v>10.94600382571844</v>
+        <v>10.93786172689113</v>
       </c>
       <c r="N2" t="n">
-        <v>202.6505835841611</v>
+        <v>202.0484450746675</v>
       </c>
       <c r="O2" t="n">
-        <v>14.23553945532663</v>
+        <v>14.21437459315982</v>
       </c>
       <c r="P2" t="n">
-        <v>359.3216791056979</v>
+        <v>359.4033359354807</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21443,28 +21543,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1012898467407615</v>
+        <v>0.09054445419622664</v>
       </c>
       <c r="J3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K3" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004717055595329978</v>
+        <v>0.003797354661400409</v>
       </c>
       <c r="M3" t="n">
-        <v>9.108932865590868</v>
+        <v>9.130816435687246</v>
       </c>
       <c r="N3" t="n">
-        <v>143.2133582310352</v>
+        <v>143.2013157227778</v>
       </c>
       <c r="O3" t="n">
-        <v>11.96717837382878</v>
+        <v>11.9666752158976</v>
       </c>
       <c r="P3" t="n">
-        <v>362.0706858774519</v>
+        <v>362.1688550474162</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21521,28 +21621,28 @@
         <v>0.0382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1200847549263385</v>
+        <v>0.1096499166106598</v>
       </c>
       <c r="J4" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K4" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008222533471665017</v>
+        <v>0.006904188381843257</v>
       </c>
       <c r="M4" t="n">
-        <v>7.740192408631675</v>
+        <v>7.767901902112571</v>
       </c>
       <c r="N4" t="n">
-        <v>113.850127582773</v>
+        <v>113.9291433361185</v>
       </c>
       <c r="O4" t="n">
-        <v>10.67005752481086</v>
+        <v>10.67375956896718</v>
       </c>
       <c r="P4" t="n">
-        <v>363.5783266829618</v>
+        <v>363.6746694613294</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21599,28 +21699,28 @@
         <v>0.0403</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1224560242924566</v>
+        <v>0.1097677161435461</v>
       </c>
       <c r="J5" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K5" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005009071643712781</v>
+        <v>0.00405490603126768</v>
       </c>
       <c r="M5" t="n">
-        <v>10.3369625403819</v>
+        <v>10.34979728542978</v>
       </c>
       <c r="N5" t="n">
-        <v>194.9716069959308</v>
+        <v>194.9591225642312</v>
       </c>
       <c r="O5" t="n">
-        <v>13.96322337413288</v>
+        <v>13.96277632006727</v>
       </c>
       <c r="P5" t="n">
-        <v>357.6030178124959</v>
+        <v>357.7201664278236</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21677,28 +21777,28 @@
         <v>0.0402</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1878714370782716</v>
+        <v>0.163584252629993</v>
       </c>
       <c r="J6" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K6" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008723975969089692</v>
+        <v>0.006620034845143175</v>
       </c>
       <c r="M6" t="n">
-        <v>12.21373696641238</v>
+        <v>12.26997233885767</v>
       </c>
       <c r="N6" t="n">
-        <v>260.9541807986687</v>
+        <v>263.0152491955728</v>
       </c>
       <c r="O6" t="n">
-        <v>16.15407629048064</v>
+        <v>16.21774488625261</v>
       </c>
       <c r="P6" t="n">
-        <v>354.9856224387186</v>
+        <v>355.209799509507</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21755,28 +21855,28 @@
         <v>0.0688</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09996743632100014</v>
+        <v>0.08784554593056781</v>
       </c>
       <c r="J7" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K7" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003022898465247281</v>
+        <v>0.002352992526067021</v>
       </c>
       <c r="M7" t="n">
-        <v>11.14394601691157</v>
+        <v>11.15022044612349</v>
       </c>
       <c r="N7" t="n">
-        <v>215.7386295724692</v>
+        <v>215.5438081715543</v>
       </c>
       <c r="O7" t="n">
-        <v>14.68804376261417</v>
+        <v>14.68141029232391</v>
       </c>
       <c r="P7" t="n">
-        <v>358.1986561953705</v>
+        <v>358.3105751886458</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21833,28 +21933,28 @@
         <v>0.0762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09382530963163442</v>
+        <v>0.08431162027769923</v>
       </c>
       <c r="J8" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K8" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003191337829072438</v>
+        <v>0.002600145647102425</v>
       </c>
       <c r="M8" t="n">
-        <v>10.31248860156281</v>
+        <v>10.31103830043185</v>
       </c>
       <c r="N8" t="n">
-        <v>179.981645640803</v>
+        <v>179.6330312931346</v>
       </c>
       <c r="O8" t="n">
-        <v>13.41572382097973</v>
+        <v>13.40272477122225</v>
       </c>
       <c r="P8" t="n">
-        <v>360.8727849563894</v>
+        <v>360.9606229503433</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21911,28 +22011,28 @@
         <v>0.0827</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1206382126455537</v>
+        <v>0.1101017150031278</v>
       </c>
       <c r="J9" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K9" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004471252259434677</v>
+        <v>0.003758358767815273</v>
       </c>
       <c r="M9" t="n">
-        <v>10.7965798622986</v>
+        <v>10.78473471135032</v>
       </c>
       <c r="N9" t="n">
-        <v>212.3175508948644</v>
+        <v>211.92050418072</v>
       </c>
       <c r="O9" t="n">
-        <v>14.57112044061349</v>
+        <v>14.55748962495663</v>
       </c>
       <c r="P9" t="n">
-        <v>363.4742995702198</v>
+        <v>363.5713114643032</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21989,28 +22089,28 @@
         <v>0.0687</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1603843632705509</v>
+        <v>0.1441558988991201</v>
       </c>
       <c r="J10" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K10" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009307637247484402</v>
+        <v>0.007554251624550812</v>
       </c>
       <c r="M10" t="n">
-        <v>10.10426225875503</v>
+        <v>10.12012423370335</v>
       </c>
       <c r="N10" t="n">
-        <v>180.4324943476915</v>
+        <v>181.0912808092365</v>
       </c>
       <c r="O10" t="n">
-        <v>13.43251630736741</v>
+        <v>13.45701604402835</v>
       </c>
       <c r="P10" t="n">
-        <v>367.6931333480196</v>
+        <v>367.8414136774302</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22067,28 +22167,28 @@
         <v>0.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1026454321579495</v>
+        <v>0.08954543120449114</v>
       </c>
       <c r="J11" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003809593224005092</v>
+        <v>0.002920838718667773</v>
       </c>
       <c r="M11" t="n">
-        <v>9.986388975805008</v>
+        <v>9.985029576489866</v>
       </c>
       <c r="N11" t="n">
-        <v>178.0469351234804</v>
+        <v>178.1137383914251</v>
       </c>
       <c r="O11" t="n">
-        <v>13.34342291630901</v>
+        <v>13.34592590985823</v>
       </c>
       <c r="P11" t="n">
-        <v>370.0968041526095</v>
+        <v>370.2175419843881</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22145,28 +22245,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09771266077945609</v>
+        <v>0.08384313423257217</v>
       </c>
       <c r="J12" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K12" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003606085751189481</v>
+        <v>0.002670798234472138</v>
       </c>
       <c r="M12" t="n">
-        <v>9.963103533144524</v>
+        <v>9.97070430148413</v>
       </c>
       <c r="N12" t="n">
-        <v>172.0150912098286</v>
+        <v>172.2815012162036</v>
       </c>
       <c r="O12" t="n">
-        <v>13.11545238296524</v>
+        <v>13.125604794302</v>
       </c>
       <c r="P12" t="n">
-        <v>371.6245629567712</v>
+        <v>371.7526295579587</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22223,28 +22323,28 @@
         <v>0.0911</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09471672113129027</v>
+        <v>0.08335159172199542</v>
       </c>
       <c r="J13" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K13" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003917653453711201</v>
+        <v>0.003056262402864163</v>
       </c>
       <c r="M13" t="n">
-        <v>9.266517580572391</v>
+        <v>9.264521450832127</v>
       </c>
       <c r="N13" t="n">
-        <v>147.1408589078767</v>
+        <v>147.1517231781123</v>
       </c>
       <c r="O13" t="n">
-        <v>12.13016318554193</v>
+        <v>12.1306109977244</v>
       </c>
       <c r="P13" t="n">
-        <v>370.3692880694662</v>
+        <v>370.4753299949651</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22301,28 +22401,28 @@
         <v>0.0549</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1789105968164776</v>
+        <v>0.1595257114253586</v>
       </c>
       <c r="J14" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K14" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008711748611921033</v>
+        <v>0.006957230837174588</v>
       </c>
       <c r="M14" t="n">
-        <v>11.91059322414437</v>
+        <v>11.92018161050833</v>
       </c>
       <c r="N14" t="n">
-        <v>234.7458608461534</v>
+        <v>235.6782166220983</v>
       </c>
       <c r="O14" t="n">
-        <v>15.32141836926834</v>
+        <v>15.35181476640786</v>
       </c>
       <c r="P14" t="n">
-        <v>367.60554028979</v>
+        <v>367.7862714874341</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22379,28 +22479,28 @@
         <v>0.0408</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3416692247270585</v>
+        <v>0.3536720803863679</v>
       </c>
       <c r="J15" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K15" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01568019079267691</v>
+        <v>0.01695531576618259</v>
       </c>
       <c r="M15" t="n">
-        <v>16.86388305257673</v>
+        <v>16.86042768966607</v>
       </c>
       <c r="N15" t="n">
-        <v>463.2750642903204</v>
+        <v>461.7027779190391</v>
       </c>
       <c r="O15" t="n">
-        <v>21.52382550315627</v>
+        <v>21.48727013650266</v>
       </c>
       <c r="P15" t="n">
-        <v>362.0815711237053</v>
+        <v>361.9684568707655</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -22457,28 +22557,28 @@
         <v>0.046</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3230539997160504</v>
+        <v>0.3168248566411998</v>
       </c>
       <c r="J16" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K16" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01591238891249802</v>
+        <v>0.01548247085501131</v>
       </c>
       <c r="M16" t="n">
-        <v>16.13731998194366</v>
+        <v>16.08911605844465</v>
       </c>
       <c r="N16" t="n">
-        <v>420.8414215023905</v>
+        <v>418.9168786769444</v>
       </c>
       <c r="O16" t="n">
-        <v>20.51441984318324</v>
+        <v>20.46745901857249</v>
       </c>
       <c r="P16" t="n">
-        <v>364.5486455970191</v>
+        <v>364.6062898411922</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -22535,28 +22635,28 @@
         <v>0.0605</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3519627049906653</v>
+        <v>0.3441857242755029</v>
       </c>
       <c r="J17" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K17" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02555470818673555</v>
+        <v>0.02471145278934561</v>
       </c>
       <c r="M17" t="n">
-        <v>13.33890757862938</v>
+        <v>13.304316916052</v>
       </c>
       <c r="N17" t="n">
-        <v>307.9992674648983</v>
+        <v>306.8504294110526</v>
       </c>
       <c r="O17" t="n">
-        <v>17.54990790474122</v>
+        <v>17.51714672573855</v>
       </c>
       <c r="P17" t="n">
-        <v>369.7568983424423</v>
+        <v>369.8287083991393</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -22613,28 +22713,28 @@
         <v>0.0604</v>
       </c>
       <c r="I18" t="n">
-        <v>0.365337131706603</v>
+        <v>0.3527342921006177</v>
       </c>
       <c r="J18" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K18" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03658287871580423</v>
+        <v>0.03443515915652706</v>
       </c>
       <c r="M18" t="n">
-        <v>12.10255523417991</v>
+        <v>12.10019629529336</v>
       </c>
       <c r="N18" t="n">
-        <v>226.7435082589127</v>
+        <v>226.5334090314001</v>
       </c>
       <c r="O18" t="n">
-        <v>15.05800479010791</v>
+        <v>15.05102684308948</v>
       </c>
       <c r="P18" t="n">
-        <v>372.9807410814328</v>
+        <v>373.0983314167861</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -22691,28 +22791,28 @@
         <v>0.0539</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2127421180147621</v>
+        <v>0.1992740770873228</v>
       </c>
       <c r="J19" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K19" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01382657037177359</v>
+        <v>0.01222963289390622</v>
       </c>
       <c r="M19" t="n">
-        <v>11.06106869376203</v>
+        <v>11.06260960552381</v>
       </c>
       <c r="N19" t="n">
-        <v>210.4823290181203</v>
+        <v>210.4991606385911</v>
       </c>
       <c r="O19" t="n">
-        <v>14.50800913351381</v>
+        <v>14.50858920221367</v>
       </c>
       <c r="P19" t="n">
-        <v>374.939394553312</v>
+        <v>375.0637539696483</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -22769,28 +22869,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3528408484012832</v>
+        <v>0.3400448637692378</v>
       </c>
       <c r="J20" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K20" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04138625536687768</v>
+        <v>0.03881408480810844</v>
       </c>
       <c r="M20" t="n">
-        <v>10.86927359155235</v>
+        <v>10.86608002810234</v>
       </c>
       <c r="N20" t="n">
-        <v>185.1210586322733</v>
+        <v>185.0929073342467</v>
       </c>
       <c r="O20" t="n">
-        <v>13.60591998478138</v>
+        <v>13.60488542157731</v>
       </c>
       <c r="P20" t="n">
-        <v>369.7731247331418</v>
+        <v>369.892151883105</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -22847,28 +22947,28 @@
         <v>0.0654</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1191076077042461</v>
+        <v>0.1054366127971407</v>
       </c>
       <c r="J21" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K21" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L21" t="n">
-        <v>0.005514848938353412</v>
+        <v>0.004347380028404735</v>
       </c>
       <c r="M21" t="n">
-        <v>9.881582861828027</v>
+        <v>9.886073476408802</v>
       </c>
       <c r="N21" t="n">
-        <v>170.1934363375286</v>
+        <v>170.4620550459917</v>
       </c>
       <c r="O21" t="n">
-        <v>13.04582064638053</v>
+        <v>13.05611178896657</v>
       </c>
       <c r="P21" t="n">
-        <v>375.8780857094847</v>
+        <v>376.0028549923238</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -22925,28 +23025,28 @@
         <v>0.0646</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1657016830974001</v>
+        <v>0.1528769770018519</v>
       </c>
       <c r="J22" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K22" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01076179945245426</v>
+        <v>0.009223683508896352</v>
       </c>
       <c r="M22" t="n">
-        <v>9.913541728983622</v>
+        <v>9.904270002281983</v>
       </c>
       <c r="N22" t="n">
-        <v>166.9071905693128</v>
+        <v>167.0709064554432</v>
       </c>
       <c r="O22" t="n">
-        <v>12.91925657959129</v>
+        <v>12.92559114529944</v>
       </c>
       <c r="P22" t="n">
-        <v>372.256736250311</v>
+        <v>372.3744495170226</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -23003,28 +23103,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.02141515765177654</v>
+        <v>-0.02954905110913589</v>
       </c>
       <c r="J23" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K23" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0001963492126373367</v>
+        <v>0.000377000095245883</v>
       </c>
       <c r="M23" t="n">
-        <v>9.214012620597588</v>
+        <v>9.193030653050529</v>
       </c>
       <c r="N23" t="n">
-        <v>153.2392427711805</v>
+        <v>152.8769074625691</v>
       </c>
       <c r="O23" t="n">
-        <v>12.37898391513538</v>
+        <v>12.36434015475832</v>
       </c>
       <c r="P23" t="n">
-        <v>375.2942589770048</v>
+        <v>375.3697576384252</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -23081,28 +23181,28 @@
         <v>0.0519</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.006521546930720858</v>
+        <v>-0.02089854145793441</v>
       </c>
       <c r="J24" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K24" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L24" t="n">
-        <v>2.399360466487366e-05</v>
+        <v>0.0002465283954345976</v>
       </c>
       <c r="M24" t="n">
-        <v>8.428367540804732</v>
+        <v>8.436883612909757</v>
       </c>
       <c r="N24" t="n">
-        <v>115.9181835074268</v>
+        <v>116.5609014410427</v>
       </c>
       <c r="O24" t="n">
-        <v>10.76653070898081</v>
+        <v>10.79633740863274</v>
       </c>
       <c r="P24" t="n">
-        <v>380.1102026275229</v>
+        <v>380.2437339576117</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -23159,28 +23259,28 @@
         <v>0.0529</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.159328981692308</v>
+        <v>-0.1770499872566328</v>
       </c>
       <c r="J25" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K25" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0105013646518668</v>
+        <v>0.01292838012710118</v>
       </c>
       <c r="M25" t="n">
-        <v>10.07660875072497</v>
+        <v>10.08369433142684</v>
       </c>
       <c r="N25" t="n">
-        <v>157.0825973783191</v>
+        <v>158.1496669072209</v>
       </c>
       <c r="O25" t="n">
-        <v>12.53325964696811</v>
+        <v>12.57575711069599</v>
       </c>
       <c r="P25" t="n">
-        <v>392.65222516311</v>
+        <v>392.8171193239142</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -23237,28 +23337,28 @@
         <v>0.042</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1170575962582673</v>
+        <v>-0.1369775444801797</v>
       </c>
       <c r="J26" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K26" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L26" t="n">
-        <v>0.003784923643020854</v>
+        <v>0.005183439205840412</v>
       </c>
       <c r="M26" t="n">
-        <v>12.54247401415544</v>
+        <v>12.56378392413461</v>
       </c>
       <c r="N26" t="n">
-        <v>231.4628889905244</v>
+        <v>232.5846195796547</v>
       </c>
       <c r="O26" t="n">
-        <v>15.21390446238323</v>
+        <v>15.250725214876</v>
       </c>
       <c r="P26" t="n">
-        <v>385.8025457708962</v>
+        <v>385.9905733840216</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -23319,28 +23419,28 @@
         <v>0.0332</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.01252343633469908</v>
+        <v>-0.02538107142638253</v>
       </c>
       <c r="J27" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K27" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L27" t="n">
-        <v>4.283072825916889e-05</v>
+        <v>0.0001771843369597903</v>
       </c>
       <c r="M27" t="n">
-        <v>12.52588223110852</v>
+        <v>12.51069985697417</v>
       </c>
       <c r="N27" t="n">
-        <v>239.8755831073548</v>
+        <v>239.6545593718847</v>
       </c>
       <c r="O27" t="n">
-        <v>15.48791732633393</v>
+        <v>15.48078032180176</v>
       </c>
       <c r="P27" t="n">
-        <v>382.4617371735492</v>
+        <v>382.5810549245911</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -23382,7 +23482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB209"/>
+  <dimension ref="A1:AB210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52489,7 +52589,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>-34.71051932004048,173.07005987242894</t>
+          <t>-34.71050381921157,173.07008146546346</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -52559,7 +52659,7 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>-34.71804720725646,173.07867866015107</t>
+          <t>-34.718023159234065,173.07870619747763</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
@@ -52618,6 +52718,148 @@
         </is>
       </c>
       <c r="AB209" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>-34.71050310924986,173.07008245445718</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>-34.711038824705334,173.07070188811014</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>-34.711581340079626,173.0713118440379</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-34.71218816311717,173.07183221287625</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-34.71282355920088,173.07231277355123</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-34.713298869710535,173.07301667469713</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-34.71382337305539,173.0736528011917</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-34.71436083643503,173.07427018491376</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-34.714918270784246,173.07485948844763</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-34.715439910384205,173.07549734973625</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-34.71598993081694,173.0760976410045</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>-34.71652052906865,173.07672427531284</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>-34.7170868717821,173.07731105466831</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>-34.71738438821408,173.07820401288825</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>-34.718028270258436,173.07870034485916</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>-34.71848336913938,173.07941284810533</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>-34.71899938052192,173.080052543685</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>-34.71948276886899,173.08072922059267</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>-34.71994214885409,173.08143242022518</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>-34.72041302256443,173.08212473258877</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>-34.72083566681581,173.0828602470311</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>-34.7211961964281,173.08364537368215</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>-34.72159486346595,173.08440174624985</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>-34.72194108151652,173.08519113536073</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>-34.72226518171175,173.08599280563274</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>-34.722424456316205,173.08687420518032</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0012/nzd0012.xlsx
+++ b/data/nzd0012/nzd0012.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB210"/>
+  <dimension ref="A1:AB212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19026,7 +19026,7 @@
         <v>362.23</v>
       </c>
       <c r="N209" t="n">
-        <v>356.55</v>
+        <v>360.88</v>
       </c>
       <c r="O209" t="n">
         <v>376.9</v>
@@ -19116,7 +19116,7 @@
         <v>360.6</v>
       </c>
       <c r="N210" t="n">
-        <v>351.65</v>
+        <v>357.83</v>
       </c>
       <c r="O210" t="n">
         <v>383.64</v>
@@ -19160,6 +19160,186 @@
       <c r="AB210" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>350.36</v>
+      </c>
+      <c r="C211" t="n">
+        <v>353.36</v>
+      </c>
+      <c r="D211" t="n">
+        <v>356.36</v>
+      </c>
+      <c r="E211" t="n">
+        <v>348.22</v>
+      </c>
+      <c r="F211" t="n">
+        <v>335.11</v>
+      </c>
+      <c r="G211" t="n">
+        <v>347.74</v>
+      </c>
+      <c r="H211" t="n">
+        <v>354.31</v>
+      </c>
+      <c r="I211" t="n">
+        <v>356.14</v>
+      </c>
+      <c r="J211" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="K211" t="n">
+        <v>359.81</v>
+      </c>
+      <c r="L211" t="n">
+        <v>360.33</v>
+      </c>
+      <c r="M211" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="N211" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="O211" t="n">
+        <v>377.84</v>
+      </c>
+      <c r="P211" t="n">
+        <v>365.03</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>371.36</v>
+      </c>
+      <c r="R211" t="n">
+        <v>370.92</v>
+      </c>
+      <c r="S211" t="n">
+        <v>367.31</v>
+      </c>
+      <c r="T211" t="n">
+        <v>365.63</v>
+      </c>
+      <c r="U211" t="n">
+        <v>363.97</v>
+      </c>
+      <c r="V211" t="n">
+        <v>362.61</v>
+      </c>
+      <c r="W211" t="n">
+        <v>366.06</v>
+      </c>
+      <c r="X211" t="n">
+        <v>365.24</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>362.92</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="C212" t="n">
+        <v>351.99</v>
+      </c>
+      <c r="D212" t="n">
+        <v>355.18</v>
+      </c>
+      <c r="E212" t="n">
+        <v>347.59</v>
+      </c>
+      <c r="F212" t="n">
+        <v>336.48</v>
+      </c>
+      <c r="G212" t="n">
+        <v>347.91</v>
+      </c>
+      <c r="H212" t="n">
+        <v>354.47</v>
+      </c>
+      <c r="I212" t="n">
+        <v>356.6</v>
+      </c>
+      <c r="J212" t="n">
+        <v>356.78</v>
+      </c>
+      <c r="K212" t="n">
+        <v>359.67</v>
+      </c>
+      <c r="L212" t="n">
+        <v>360.82</v>
+      </c>
+      <c r="M212" t="n">
+        <v>361.65</v>
+      </c>
+      <c r="N212" t="n">
+        <v>360.85</v>
+      </c>
+      <c r="O212" t="n">
+        <v>375</v>
+      </c>
+      <c r="P212" t="n">
+        <v>363.73</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>372.33</v>
+      </c>
+      <c r="R212" t="n">
+        <v>372.07</v>
+      </c>
+      <c r="S212" t="n">
+        <v>367.83</v>
+      </c>
+      <c r="T212" t="n">
+        <v>365.99</v>
+      </c>
+      <c r="U212" t="n">
+        <v>363.8</v>
+      </c>
+      <c r="V212" t="n">
+        <v>362.58</v>
+      </c>
+      <c r="W212" t="n">
+        <v>365.5</v>
+      </c>
+      <c r="X212" t="n">
+        <v>365.46</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>362.85</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>368.68</v>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19174,7 +19354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B212"/>
+  <dimension ref="A1:B214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21297,6 +21477,26 @@
       </c>
       <c r="B212" t="n">
         <v>-0.91</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -21465,28 +21665,28 @@
         <v>0.0363</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07416700232689666</v>
+        <v>0.05478135460227065</v>
       </c>
       <c r="J2" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K2" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00179030665187152</v>
+        <v>0.0009938984654084271</v>
       </c>
       <c r="M2" t="n">
-        <v>10.93786172689113</v>
+        <v>10.93308146420145</v>
       </c>
       <c r="N2" t="n">
-        <v>202.0484450746675</v>
+        <v>201.2225498557547</v>
       </c>
       <c r="O2" t="n">
-        <v>14.21437459315982</v>
+        <v>14.18529343565915</v>
       </c>
       <c r="P2" t="n">
-        <v>359.4033359354807</v>
+        <v>359.583050833189</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21543,28 +21743,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09054445419622664</v>
+        <v>0.06960806811368239</v>
       </c>
       <c r="J3" t="n">
+        <v>211</v>
+      </c>
+      <c r="K3" t="n">
         <v>209</v>
       </c>
-      <c r="K3" t="n">
-        <v>207</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.003797354661400409</v>
+        <v>0.002276668016829797</v>
       </c>
       <c r="M3" t="n">
-        <v>9.130816435687246</v>
+        <v>9.169835988679823</v>
       </c>
       <c r="N3" t="n">
-        <v>143.2013157227778</v>
+        <v>143.1570741654673</v>
       </c>
       <c r="O3" t="n">
-        <v>11.9666752158976</v>
+        <v>11.96482654138652</v>
       </c>
       <c r="P3" t="n">
-        <v>362.1688550474162</v>
+        <v>362.3609307873348</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21621,28 +21821,28 @@
         <v>0.0382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1096499166106598</v>
+        <v>0.09041342340433846</v>
       </c>
       <c r="J4" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K4" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006904188381843257</v>
+        <v>0.00476337039482233</v>
       </c>
       <c r="M4" t="n">
-        <v>7.767901902112571</v>
+        <v>7.813836424887318</v>
       </c>
       <c r="N4" t="n">
-        <v>113.9291433361185</v>
+        <v>113.936485546976</v>
       </c>
       <c r="O4" t="n">
-        <v>10.67375956896718</v>
+        <v>10.67410350085552</v>
       </c>
       <c r="P4" t="n">
-        <v>363.6746694613294</v>
+        <v>363.8530133547467</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21699,28 +21899,28 @@
         <v>0.0403</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1097677161435461</v>
+        <v>0.0871478088050107</v>
       </c>
       <c r="J5" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K5" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00405490603126768</v>
+        <v>0.002596646814859493</v>
       </c>
       <c r="M5" t="n">
-        <v>10.34979728542978</v>
+        <v>10.36081776375054</v>
       </c>
       <c r="N5" t="n">
-        <v>194.9591225642312</v>
+        <v>194.6058441655711</v>
       </c>
       <c r="O5" t="n">
-        <v>13.96277632006727</v>
+        <v>13.95011986205033</v>
       </c>
       <c r="P5" t="n">
-        <v>357.7201664278236</v>
+        <v>357.9298718776778</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21777,28 +21977,28 @@
         <v>0.0402</v>
       </c>
       <c r="I6" t="n">
-        <v>0.163584252629993</v>
+        <v>0.1207675285248378</v>
       </c>
       <c r="J6" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K6" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006620034845143175</v>
+        <v>0.003627785139561079</v>
       </c>
       <c r="M6" t="n">
-        <v>12.26997233885767</v>
+        <v>12.35217056487758</v>
       </c>
       <c r="N6" t="n">
-        <v>263.0152491955728</v>
+        <v>265.7909276648842</v>
       </c>
       <c r="O6" t="n">
-        <v>16.21774488625261</v>
+        <v>16.30309564668269</v>
       </c>
       <c r="P6" t="n">
-        <v>355.209799509507</v>
+        <v>355.6065911948333</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21855,28 +22055,28 @@
         <v>0.0688</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08784554593056781</v>
+        <v>0.06508699217415861</v>
       </c>
       <c r="J7" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K7" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002352992526067021</v>
+        <v>0.001312632546252246</v>
       </c>
       <c r="M7" t="n">
-        <v>11.15022044612349</v>
+        <v>11.15996914050826</v>
       </c>
       <c r="N7" t="n">
-        <v>215.5438081715543</v>
+        <v>215.01055780907</v>
       </c>
       <c r="O7" t="n">
-        <v>14.68141029232391</v>
+        <v>14.66323831249666</v>
       </c>
       <c r="P7" t="n">
-        <v>358.3105751886458</v>
+        <v>358.5215590602236</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21933,28 +22133,28 @@
         <v>0.0762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08431162027769923</v>
+        <v>0.06864946547570215</v>
       </c>
       <c r="J8" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K8" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002600145647102425</v>
+        <v>0.001756829107829816</v>
       </c>
       <c r="M8" t="n">
-        <v>10.31103830043185</v>
+        <v>10.29246259973444</v>
       </c>
       <c r="N8" t="n">
-        <v>179.6330312931346</v>
+        <v>178.634830713956</v>
       </c>
       <c r="O8" t="n">
-        <v>13.40272477122225</v>
+        <v>13.36543417603618</v>
       </c>
       <c r="P8" t="n">
-        <v>360.9606229503433</v>
+        <v>361.1058191065064</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22011,28 +22211,28 @@
         <v>0.0827</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1101017150031278</v>
+        <v>0.09198428016367408</v>
       </c>
       <c r="J9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K9" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003758358767815273</v>
+        <v>0.002673263651807201</v>
       </c>
       <c r="M9" t="n">
-        <v>10.78473471135032</v>
+        <v>10.74958751177874</v>
       </c>
       <c r="N9" t="n">
-        <v>211.92050418072</v>
+        <v>210.8411506443091</v>
       </c>
       <c r="O9" t="n">
-        <v>14.55748962495663</v>
+        <v>14.52037019653112</v>
       </c>
       <c r="P9" t="n">
-        <v>363.5713114643032</v>
+        <v>363.738800452147</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22089,28 +22289,28 @@
         <v>0.0687</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1441558988991201</v>
+        <v>0.1171739955016052</v>
       </c>
       <c r="J10" t="n">
+        <v>211</v>
+      </c>
+      <c r="K10" t="n">
         <v>209</v>
       </c>
-      <c r="K10" t="n">
-        <v>207</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.007554251624550812</v>
+        <v>0.005055344438249398</v>
       </c>
       <c r="M10" t="n">
-        <v>10.12012423370335</v>
+        <v>10.14160628359154</v>
       </c>
       <c r="N10" t="n">
-        <v>181.0912808092365</v>
+        <v>181.5272809532059</v>
       </c>
       <c r="O10" t="n">
-        <v>13.45701604402835</v>
+        <v>13.47320603840103</v>
       </c>
       <c r="P10" t="n">
-        <v>367.8414136774302</v>
+        <v>368.0889527029656</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22167,28 +22367,28 @@
         <v>0.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08954543120449114</v>
+        <v>0.06596978175924201</v>
       </c>
       <c r="J11" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002920838718667773</v>
+        <v>0.00161038888943843</v>
       </c>
       <c r="M11" t="n">
-        <v>9.985029576489866</v>
+        <v>9.977076765778341</v>
       </c>
       <c r="N11" t="n">
-        <v>178.1137383914251</v>
+        <v>177.9460031927675</v>
       </c>
       <c r="O11" t="n">
-        <v>13.34592590985823</v>
+        <v>13.33964029472937</v>
       </c>
       <c r="P11" t="n">
-        <v>370.2175419843881</v>
+        <v>370.4356913842406</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22245,28 +22445,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08384313423257217</v>
+        <v>0.05989991867182578</v>
       </c>
       <c r="J12" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K12" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002670798234472138</v>
+        <v>0.001382251026569303</v>
       </c>
       <c r="M12" t="n">
-        <v>9.97070430148413</v>
+        <v>9.974064818822178</v>
       </c>
       <c r="N12" t="n">
-        <v>172.2815012162036</v>
+        <v>172.3076189703094</v>
       </c>
       <c r="O12" t="n">
-        <v>13.125604794302</v>
+        <v>13.12659967281357</v>
       </c>
       <c r="P12" t="n">
-        <v>371.7526295579587</v>
+        <v>371.9746056633896</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22323,28 +22523,28 @@
         <v>0.0911</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08335159172199542</v>
+        <v>0.06283213167251633</v>
       </c>
       <c r="J13" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K13" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003056262402864163</v>
+        <v>0.00176377543514683</v>
       </c>
       <c r="M13" t="n">
-        <v>9.264521450832127</v>
+        <v>9.251629391350207</v>
       </c>
       <c r="N13" t="n">
-        <v>147.1517231781123</v>
+        <v>146.9483025940067</v>
       </c>
       <c r="O13" t="n">
-        <v>12.1306109977244</v>
+        <v>12.12222350041471</v>
       </c>
       <c r="P13" t="n">
-        <v>370.4753299949651</v>
+        <v>370.6675492623928</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22401,28 +22601,28 @@
         <v>0.0549</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1595257114253586</v>
+        <v>0.1479485331958375</v>
       </c>
       <c r="J14" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K14" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L14" t="n">
-        <v>0.006957230837174588</v>
+        <v>0.006135451105231615</v>
       </c>
       <c r="M14" t="n">
-        <v>11.92018161050833</v>
+        <v>11.84440185708354</v>
       </c>
       <c r="N14" t="n">
-        <v>235.6782166220983</v>
+        <v>233.0629773215846</v>
       </c>
       <c r="O14" t="n">
-        <v>15.35181476640786</v>
+        <v>15.26640027385581</v>
       </c>
       <c r="P14" t="n">
-        <v>367.7862714874341</v>
+        <v>367.8951527364415</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22479,28 +22679,28 @@
         <v>0.0408</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3536720803863679</v>
+        <v>0.362949172130787</v>
       </c>
       <c r="J15" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K15" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01695531576618259</v>
+        <v>0.01825020511750708</v>
       </c>
       <c r="M15" t="n">
-        <v>16.86042768966607</v>
+        <v>16.75467802170556</v>
       </c>
       <c r="N15" t="n">
-        <v>461.7027779190391</v>
+        <v>457.3610398699051</v>
       </c>
       <c r="O15" t="n">
-        <v>21.48727013650266</v>
+        <v>21.38600102566876</v>
       </c>
       <c r="P15" t="n">
-        <v>361.9684568707655</v>
+        <v>361.8807155293289</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -22557,28 +22757,28 @@
         <v>0.046</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3168248566411998</v>
+        <v>0.3011922164613263</v>
       </c>
       <c r="J16" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K16" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01548247085501131</v>
+        <v>0.01430162674777147</v>
       </c>
       <c r="M16" t="n">
-        <v>16.08911605844465</v>
+        <v>16.01064024477206</v>
       </c>
       <c r="N16" t="n">
-        <v>418.9168786769444</v>
+        <v>415.6097673459809</v>
       </c>
       <c r="O16" t="n">
-        <v>20.46745901857249</v>
+        <v>20.38650944487508</v>
       </c>
       <c r="P16" t="n">
-        <v>364.6062898411922</v>
+        <v>364.7512330357444</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -22635,28 +22835,28 @@
         <v>0.0605</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3441857242755029</v>
+        <v>0.3312273378106029</v>
       </c>
       <c r="J17" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K17" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02471145278934561</v>
+        <v>0.02339765653963755</v>
       </c>
       <c r="M17" t="n">
-        <v>13.304316916052</v>
+        <v>13.22577848148044</v>
       </c>
       <c r="N17" t="n">
-        <v>306.8504294110526</v>
+        <v>304.3949231155581</v>
       </c>
       <c r="O17" t="n">
-        <v>17.51714672573855</v>
+        <v>17.44691729548685</v>
       </c>
       <c r="P17" t="n">
-        <v>369.8287083991393</v>
+        <v>369.9488389232276</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -22713,28 +22913,28 @@
         <v>0.0604</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3527342921006177</v>
+        <v>0.3327356243119911</v>
       </c>
       <c r="J18" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K18" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03443515915652706</v>
+        <v>0.03127905987543333</v>
       </c>
       <c r="M18" t="n">
-        <v>12.10019629529336</v>
+        <v>12.07176279771439</v>
       </c>
       <c r="N18" t="n">
-        <v>226.5334090314001</v>
+        <v>225.5041548944821</v>
       </c>
       <c r="O18" t="n">
-        <v>15.05102684308948</v>
+        <v>15.01679575989772</v>
       </c>
       <c r="P18" t="n">
-        <v>373.0983314167861</v>
+        <v>373.2856678456593</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -22791,28 +22991,28 @@
         <v>0.0539</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1992740770873228</v>
+        <v>0.1763426149564129</v>
       </c>
       <c r="J19" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K19" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01222963289390622</v>
+        <v>0.009746365281106617</v>
       </c>
       <c r="M19" t="n">
-        <v>11.06260960552381</v>
+        <v>11.0513640422919</v>
       </c>
       <c r="N19" t="n">
-        <v>210.4991606385911</v>
+        <v>210.0187021350008</v>
       </c>
       <c r="O19" t="n">
-        <v>14.50858920221367</v>
+        <v>14.49202201678568</v>
       </c>
       <c r="P19" t="n">
-        <v>375.0637539696483</v>
+        <v>375.2763498244672</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -22869,28 +23069,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3400448637692378</v>
+        <v>0.3155676264747355</v>
       </c>
       <c r="J20" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K20" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03881408480810844</v>
+        <v>0.03407261381705984</v>
       </c>
       <c r="M20" t="n">
-        <v>10.86608002810234</v>
+        <v>10.85648932265847</v>
       </c>
       <c r="N20" t="n">
-        <v>185.0929073342467</v>
+        <v>184.9465489070206</v>
       </c>
       <c r="O20" t="n">
-        <v>13.60488542157731</v>
+        <v>13.59950546553148</v>
       </c>
       <c r="P20" t="n">
-        <v>369.892151883105</v>
+        <v>370.1207337670896</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -22947,28 +23147,28 @@
         <v>0.0654</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1054366127971407</v>
+        <v>0.07905055207397119</v>
       </c>
       <c r="J21" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K21" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L21" t="n">
-        <v>0.004347380028404735</v>
+        <v>0.002472417048363207</v>
       </c>
       <c r="M21" t="n">
-        <v>9.886073476408802</v>
+        <v>9.89320341235153</v>
       </c>
       <c r="N21" t="n">
-        <v>170.4620550459917</v>
+        <v>170.9117616378412</v>
       </c>
       <c r="O21" t="n">
-        <v>13.05611178896657</v>
+        <v>13.07332251716606</v>
       </c>
       <c r="P21" t="n">
-        <v>376.0028549923238</v>
+        <v>376.2446786781819</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -23025,28 +23225,28 @@
         <v>0.0646</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1528769770018519</v>
+        <v>0.1285000488287809</v>
       </c>
       <c r="J22" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K22" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L22" t="n">
-        <v>0.009223683508896352</v>
+        <v>0.006607126099840488</v>
       </c>
       <c r="M22" t="n">
-        <v>9.904270002281983</v>
+        <v>9.883958729650642</v>
       </c>
       <c r="N22" t="n">
-        <v>167.0709064554432</v>
+        <v>167.2663071716092</v>
       </c>
       <c r="O22" t="n">
-        <v>12.92559114529944</v>
+        <v>12.93314761268923</v>
       </c>
       <c r="P22" t="n">
-        <v>372.3744495170226</v>
+        <v>372.5991274831857</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -23103,28 +23303,28 @@
         <v>0.0611</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.02954905110913589</v>
+        <v>-0.04509173597736683</v>
       </c>
       <c r="J23" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K23" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L23" t="n">
-        <v>0.000377000095245883</v>
+        <v>0.0008926543538214649</v>
       </c>
       <c r="M23" t="n">
-        <v>9.193030653050529</v>
+        <v>9.162612084970235</v>
       </c>
       <c r="N23" t="n">
-        <v>152.8769074625691</v>
+        <v>152.1203010933173</v>
       </c>
       <c r="O23" t="n">
-        <v>12.36434015475832</v>
+        <v>12.33370589455243</v>
       </c>
       <c r="P23" t="n">
-        <v>375.3697576384252</v>
+        <v>375.514628916715</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -23181,28 +23381,28 @@
         <v>0.0519</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.02089854145793441</v>
+        <v>-0.04623811214306355</v>
       </c>
       <c r="J24" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K24" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0002465283954345976</v>
+        <v>0.001212287470512829</v>
       </c>
       <c r="M24" t="n">
-        <v>8.436883612909757</v>
+        <v>8.44829962248283</v>
       </c>
       <c r="N24" t="n">
-        <v>116.5609014410427</v>
+        <v>117.3566734664564</v>
       </c>
       <c r="O24" t="n">
-        <v>10.79633740863274</v>
+        <v>10.83312851702851</v>
       </c>
       <c r="P24" t="n">
-        <v>380.2437339576117</v>
+        <v>380.480052590266</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -23259,28 +23459,28 @@
         <v>0.0529</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1770499872566328</v>
+        <v>-0.2062666373928132</v>
       </c>
       <c r="J25" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K25" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01292838012710118</v>
+        <v>0.01756521012177337</v>
       </c>
       <c r="M25" t="n">
-        <v>10.08369433142684</v>
+        <v>10.0767957975358</v>
       </c>
       <c r="N25" t="n">
-        <v>158.1496669072209</v>
+        <v>159.1671999645497</v>
       </c>
       <c r="O25" t="n">
-        <v>12.57575711069599</v>
+        <v>12.61614838072816</v>
       </c>
       <c r="P25" t="n">
-        <v>392.8171193239142</v>
+        <v>393.0901135622916</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -23337,28 +23537,28 @@
         <v>0.042</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1369775444801797</v>
+        <v>-0.1718543335034768</v>
       </c>
       <c r="J26" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K26" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L26" t="n">
-        <v>0.005183439205840412</v>
+        <v>0.008191078711341504</v>
       </c>
       <c r="M26" t="n">
-        <v>12.56378392413461</v>
+        <v>12.58420512475388</v>
       </c>
       <c r="N26" t="n">
-        <v>232.5846195796547</v>
+        <v>233.86899799728</v>
       </c>
       <c r="O26" t="n">
-        <v>15.250725214876</v>
+        <v>15.29277600690208</v>
       </c>
       <c r="P26" t="n">
-        <v>385.9905733840216</v>
+        <v>386.3211121831735</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -23419,28 +23619,28 @@
         <v>0.0332</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.02538107142638253</v>
+        <v>-0.04824530203719529</v>
       </c>
       <c r="J27" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K27" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0001771843369597903</v>
+        <v>0.0006499827441954764</v>
       </c>
       <c r="M27" t="n">
-        <v>12.51069985697417</v>
+        <v>12.47273861155904</v>
       </c>
       <c r="N27" t="n">
-        <v>239.6545593718847</v>
+        <v>238.8736989531304</v>
       </c>
       <c r="O27" t="n">
-        <v>15.48078032180176</v>
+        <v>15.45553942614526</v>
       </c>
       <c r="P27" t="n">
-        <v>382.5810549245911</v>
+        <v>382.7941174997167</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -23482,7 +23682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB210"/>
+  <dimension ref="A1:AB212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52649,7 +52849,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>-34.71705476433567,173.07734782105</t>
+          <t>-34.71702639182773,173.0773803105024</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -52791,7 +52991,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>-34.7170868717821,173.07731105466831</t>
+          <t>-34.71704637708249,173.0773574253246</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -52862,6 +53062,290 @@
       <c r="AB210" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>-34.710496364613086,173.070091849897</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>-34.71103574819021,173.07070617376183</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>-34.71157512785744,173.0713204977836</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-34.712180412603345,173.07184300950348</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-34.712815098690676,173.07232455924455</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-34.71329762548221,173.07301840360128</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-34.71381501599679,173.07366426120402</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-34.71435507146841,173.0742780062574</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-34.71490602017901,173.07487610885687</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-34.71543444562817,173.07550476376124</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-34.715982269173224,173.0761078027114</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-34.716518049807256,173.07672729624684</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-34.71703078203161,173.07737528326757</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-34.71742239316676,173.0781604936094</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>-34.71801346139219,173.07871730244403</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>-34.71847910993344,173.0794177252893</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>-34.71898728212347,173.08006531994363</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>-34.719472969946295,173.0807386875755</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>-34.71994306781907,173.08143153865697</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>-34.72041294975602,173.08212479703</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>-34.720834377075974,173.0828612507058</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>-34.72119373633545,173.08364720055206</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>-34.721585868726066,173.08440842572162</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>-34.7219209204058,173.08520310860462</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>-34.72224906564414,173.08599952297445</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>-34.722412402125165,173.08687875089672</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>-34.71049524050689,173.07009341580348</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>-34.711043853623956,173.07069488271725</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>-34.711582109211854,173.07131077262164</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-34.7121841399498,173.07183781723262</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-34.71280699316583,173.07233585043096</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-34.71329661824975,173.0730198031903</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-34.713814060904326,173.0736655709196</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-34.7143523090884,173.07428175398417</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-34.714901936643415,173.0748816489922</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-34.715435286359885,173.07550362314208</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-34.71597928964488,173.07611175448577</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>-34.71651385413395,173.0767324085963</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>-34.71702658840403,173.07738008540235</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>-34.71744100248268,173.0781391841549</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>-34.71802197976686,173.07870754808178</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>-34.71847275388729,173.07942500354756</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>-34.718979465741725,173.080073574266</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>-34.71946930416206,173.08074222918</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>-34.719940522992985,173.08143397992274</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>-34.720414187499,173.08212370152899</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>-34.72083460467712,173.08286107358674</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>-34.721198041497566,173.08364400352966</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>-34.721584177407415,173.0844096816905</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>-34.72191768167304,173.08520503201675</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>-34.72224966253553,173.08599927418405</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>-34.72241903193026,173.08687625075285</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
